--- a/diseases/d002/2010-2014.xlsx
+++ b/diseases/d002/2010-2014.xlsx
@@ -1436,9 +1436,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2028,9 +2025,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -2620,9 +2614,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3212,9 +3203,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3804,9 +3792,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4396,9 +4381,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -5136,9 +5118,6 @@
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -5728,9 +5707,6 @@
       <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -6468,9 +6444,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7208,9 +7181,6 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -7948,9 +7918,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8540,9 +8507,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9359,9 +9323,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9951,9 +9912,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10543,9 +10501,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11283,9 +11238,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12023,9 +11975,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12615,9 +12564,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13207,9 +13153,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -13799,9 +13742,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -14539,9 +14479,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15131,9 +15068,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15723,9 +15657,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16463,9 +16394,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -17282,9 +17210,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17874,9 +17799,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18466,9 +18388,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -19058,9 +18977,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -19650,9 +19566,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -20242,9 +20155,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -20834,9 +20744,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21426,9 +21333,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -22166,9 +22070,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -23350,9 +23251,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -24682,9 +24580,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -26014,9 +25909,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -27573,9 +27465,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -29053,9 +28942,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -30237,9 +30123,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -31421,9 +31304,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -32605,9 +32485,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -33937,9 +33814,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -35121,9 +34995,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -36453,9 +36324,6 @@
       <c r="O241" t="n">
         <v>1</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -37933,9 +37801,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -39265,9 +39130,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -40745,9 +40607,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -41929,9 +41788,6 @@
       <c r="O278" t="n">
         <v>2</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -43488,9 +43344,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -44820,9 +44673,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -46004,9 +45854,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -47188,9 +47035,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -48372,9 +48216,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -49852,9 +49693,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -51184,9 +51022,6 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
@@ -52516,9 +52351,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -53848,9 +53680,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -55032,9 +54861,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -56364,9 +56190,6 @@
       <c r="O375" t="n">
         <v>0</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
@@ -57546,9 +57369,6 @@
         <v>0</v>
       </c>
       <c r="O383" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q383" t="n">
         <v>0</v>
       </c>
       <c r="R383" t="n">
